--- a/source/bin/excel/amulet.xlsx
+++ b/source/bin/excel/amulet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\雀魂策划\liqi-excel\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Work\Git\liqi-excel\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52BEFDE2-EF3B-4797-AD32-4020E07AE560}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83C0EA61-0389-45E0-80E1-FDA33FB6DF4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" firstSheet="3" activeTab="4" xr2:uid="{DC9447C4-71D8-6D42-B8C0-4F33987E6336}"/>
+    <workbookView xWindow="885" yWindow="-120" windowWidth="28035" windowHeight="16440" firstSheet="3" activeTab="4" xr2:uid="{DC9447C4-71D8-6D42-B8C0-4F33987E6336}"/>
   </bookViews>
   <sheets>
     <sheet name="export" sheetId="2" r:id="rId1"/>
@@ -30,21 +30,10 @@
     <sheet name="amulet_task" sheetId="13" r:id="rId15"/>
     <sheet name="amulet_large_number" sheetId="17" r:id="rId16"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -89,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2480" uniqueCount="1638">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2476" uniqueCount="1637">
   <si>
     <t>group</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -4488,9 +4477,6 @@
   </si>
   <si>
     <t>tag_id[0]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25084011	</t>
   </si>
   <si>
     <t>x15番。关卡结束时，本护身符消失</t>
@@ -6268,16 +6254,16 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
+        <v>1633</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>1634</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>1635</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>1637</v>
+        <v>1636</v>
       </c>
     </row>
   </sheetData>
@@ -7436,10 +7422,10 @@
         <v>316</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>1621</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>1622</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>1623</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>308</v>
@@ -7474,10 +7460,10 @@
         <v>300</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>383</v>
@@ -7882,7 +7868,7 @@
         <v>1</v>
       </c>
       <c r="N15" s="16" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="O15" s="3" t="s">
         <v>361</v>
@@ -10180,13 +10166,13 @@
         <v>57</v>
       </c>
       <c r="B1" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="C1" t="s">
+        <v>1631</v>
+      </c>
+      <c r="D1" t="s">
         <v>1632</v>
-      </c>
-      <c r="D1" t="s">
-        <v>1633</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -10194,13 +10180,13 @@
         <v>43</v>
       </c>
       <c r="B2" t="s">
-        <v>1636</v>
+        <v>1635</v>
       </c>
       <c r="C2" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="D2" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -10208,13 +10194,13 @@
         <v>30</v>
       </c>
       <c r="B3" t="s">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="C3" t="s">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="D3" t="s">
-        <v>1630</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -11136,7 +11122,7 @@
         <v>54</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>1356</v>
@@ -11204,7 +11190,7 @@
         <v>40</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>1357</v>
@@ -11663,7 +11649,7 @@
         <v>28</v>
       </c>
       <c r="D3" s="26" t="s">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>87</v>
@@ -20906,7 +20892,7 @@
         <v>1010</v>
       </c>
       <c r="D268" s="25" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="F268" s="3">
         <v>10</v>
@@ -20941,7 +20927,7 @@
         <v>1011</v>
       </c>
       <c r="D269" s="25" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="F269" s="3">
         <v>10</v>
@@ -20976,7 +20962,7 @@
         <v>1012</v>
       </c>
       <c r="D270" s="25" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="E270" s="3">
         <v>113</v>
@@ -21014,7 +21000,7 @@
         <v>1013</v>
       </c>
       <c r="D271" s="25" t="s">
-        <v>1616</v>
+        <v>1615</v>
       </c>
       <c r="F271" s="3">
         <v>10</v>
@@ -21049,7 +21035,7 @@
         <v>1014</v>
       </c>
       <c r="D272" s="25" t="s">
-        <v>1615</v>
+        <v>1614</v>
       </c>
       <c r="F272" s="3">
         <v>10</v>
@@ -21084,7 +21070,7 @@
         <v>1015</v>
       </c>
       <c r="D273" s="25" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
       <c r="E273" s="3">
         <v>113</v>
@@ -21122,7 +21108,7 @@
         <v>1016</v>
       </c>
       <c r="D274" s="25" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="F274" s="3">
         <v>10</v>
@@ -21157,7 +21143,7 @@
         <v>1017</v>
       </c>
       <c r="D275" s="25" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
       <c r="F275" s="3">
         <v>10</v>
@@ -21192,7 +21178,7 @@
         <v>1018</v>
       </c>
       <c r="D276" s="25" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="E276" s="3">
         <v>113</v>
@@ -21230,7 +21216,7 @@
         <v>1019</v>
       </c>
       <c r="D277" s="25" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="F277" s="3">
         <v>10</v>
@@ -21265,7 +21251,7 @@
         <v>1020</v>
       </c>
       <c r="D278" s="25" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
       <c r="F278" s="3">
         <v>10</v>
@@ -21300,7 +21286,7 @@
         <v>1021</v>
       </c>
       <c r="D279" s="27" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="E279" s="3">
         <v>103</v>
@@ -21338,7 +21324,7 @@
         <v>1022</v>
       </c>
       <c r="D280" s="27" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="F280" s="3">
         <v>10</v>
@@ -21373,7 +21359,7 @@
         <v>1023</v>
       </c>
       <c r="D281" s="27" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="F281" s="3">
         <v>10</v>
@@ -21408,7 +21394,7 @@
         <v>1024</v>
       </c>
       <c r="D282" s="27" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="E282" s="3">
         <v>103</v>
@@ -21446,7 +21432,7 @@
         <v>1025</v>
       </c>
       <c r="D283" s="27" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="F283" s="3">
         <v>10</v>
@@ -21481,7 +21467,7 @@
         <v>1026</v>
       </c>
       <c r="D284" s="27" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="F284" s="3">
         <v>10</v>
@@ -21516,7 +21502,7 @@
         <v>1027</v>
       </c>
       <c r="D285" s="27" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="E285" s="3">
         <v>103</v>
@@ -21554,7 +21540,7 @@
         <v>1028</v>
       </c>
       <c r="D286" s="27" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="F286" s="3">
         <v>10</v>
@@ -21589,7 +21575,7 @@
         <v>1029</v>
       </c>
       <c r="D287" s="27" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="F287" s="3">
         <v>10</v>
@@ -21624,7 +21610,7 @@
         <v>1030</v>
       </c>
       <c r="D288" s="27" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="E288" s="3">
         <v>103</v>
@@ -21662,7 +21648,7 @@
         <v>1031</v>
       </c>
       <c r="D289" s="27" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="F289" s="3">
         <v>10</v>
@@ -21697,7 +21683,7 @@
         <v>1032</v>
       </c>
       <c r="D290" s="27" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="F290" s="3">
         <v>10</v>
@@ -21732,7 +21718,7 @@
         <v>1033</v>
       </c>
       <c r="D291" s="27" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="E291" s="3">
         <v>103</v>
@@ -21770,7 +21756,7 @@
         <v>1034</v>
       </c>
       <c r="D292" s="27" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="F292" s="3">
         <v>10</v>
@@ -21805,7 +21791,7 @@
         <v>1035</v>
       </c>
       <c r="D293" s="27" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="F293" s="3">
         <v>10</v>
@@ -21840,7 +21826,7 @@
         <v>1036</v>
       </c>
       <c r="D294" s="27" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="E294" s="3">
         <v>103</v>
@@ -21878,7 +21864,7 @@
         <v>1037</v>
       </c>
       <c r="D295" s="27" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="F295" s="3">
         <v>10</v>
@@ -21913,7 +21899,7 @@
         <v>1038</v>
       </c>
       <c r="D296" s="27" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F296" s="3">
         <v>10</v>
@@ -21948,7 +21934,7 @@
         <v>1039</v>
       </c>
       <c r="D297" s="27" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="E297" s="3">
         <v>103</v>
@@ -21986,7 +21972,7 @@
         <v>1040</v>
       </c>
       <c r="D298" s="27" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="F298" s="3">
         <v>10</v>
@@ -22021,7 +22007,7 @@
         <v>1041</v>
       </c>
       <c r="D299" s="27" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="F299" s="3">
         <v>10</v>
@@ -22056,7 +22042,7 @@
         <v>1042</v>
       </c>
       <c r="D300" s="27" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="E300" s="3">
         <v>103</v>
@@ -22094,7 +22080,7 @@
         <v>1043</v>
       </c>
       <c r="D301" s="27" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="F301" s="3">
         <v>10</v>
@@ -22129,7 +22115,7 @@
         <v>1044</v>
       </c>
       <c r="D302" s="27" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="F302" s="3">
         <v>10</v>
@@ -22164,7 +22150,7 @@
         <v>1045</v>
       </c>
       <c r="D303" s="27" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="E303" s="3">
         <v>103</v>
@@ -22202,7 +22188,7 @@
         <v>1046</v>
       </c>
       <c r="D304" s="27" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="F304" s="3">
         <v>10</v>
@@ -22237,7 +22223,7 @@
         <v>1047</v>
       </c>
       <c r="D305" s="27" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
       <c r="F305" s="3">
         <v>10</v>
@@ -22272,7 +22258,7 @@
         <v>1048</v>
       </c>
       <c r="D306" s="27" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
       <c r="E306" s="3">
         <v>103</v>
@@ -22310,7 +22296,7 @@
         <v>1049</v>
       </c>
       <c r="D307" s="27" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="F307" s="3">
         <v>10</v>
@@ -22345,7 +22331,7 @@
         <v>1050</v>
       </c>
       <c r="D308" s="27" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
       <c r="F308" s="3">
         <v>10</v>
@@ -22380,7 +22366,7 @@
         <v>1051</v>
       </c>
       <c r="D309" s="27" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="E309" s="3">
         <v>103</v>
@@ -22418,7 +22404,7 @@
         <v>1052</v>
       </c>
       <c r="D310" s="27" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="F310" s="3">
         <v>10</v>
@@ -22453,7 +22439,7 @@
         <v>1053</v>
       </c>
       <c r="D311" s="27" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="F311" s="3">
         <v>10</v>
@@ -22488,7 +22474,7 @@
         <v>1054</v>
       </c>
       <c r="D312" s="27" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="E312" s="3">
         <v>103</v>
@@ -22526,7 +22512,7 @@
         <v>1055</v>
       </c>
       <c r="D313" s="27" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="F313" s="3">
         <v>10</v>
@@ -22561,7 +22547,7 @@
         <v>1056</v>
       </c>
       <c r="D314" s="27" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="F314" s="3">
         <v>10</v>
@@ -22596,7 +22582,7 @@
         <v>1057</v>
       </c>
       <c r="D315" s="27" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
       <c r="E315" s="3">
         <v>103</v>
@@ -22634,7 +22620,7 @@
         <v>1058</v>
       </c>
       <c r="D316" s="27" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="F316" s="3">
         <v>10</v>
@@ -22669,7 +22655,7 @@
         <v>1059</v>
       </c>
       <c r="D317" s="27" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="F317" s="3">
         <v>10</v>
@@ -22704,7 +22690,7 @@
         <v>1060</v>
       </c>
       <c r="D318" s="27" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="E318" s="3">
         <v>103</v>
@@ -22742,7 +22728,7 @@
         <v>1061</v>
       </c>
       <c r="D319" s="27" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="F319" s="3">
         <v>10</v>
@@ -22777,7 +22763,7 @@
         <v>1062</v>
       </c>
       <c r="D320" s="27" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="F320" s="3">
         <v>10</v>
@@ -22812,7 +22798,7 @@
         <v>1063</v>
       </c>
       <c r="D321" s="27" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="E321" s="3">
         <v>103</v>
@@ -22850,7 +22836,7 @@
         <v>1064</v>
       </c>
       <c r="D322" s="27" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="F322" s="3">
         <v>10</v>
@@ -22885,7 +22871,7 @@
         <v>1065</v>
       </c>
       <c r="D323" s="27" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="F323" s="3">
         <v>10</v>
@@ -22920,7 +22906,7 @@
         <v>1066</v>
       </c>
       <c r="D324" s="27" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="E324" s="3">
         <v>103</v>
@@ -22958,7 +22944,7 @@
         <v>1067</v>
       </c>
       <c r="D325" s="27" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="F325" s="3">
         <v>10</v>
@@ -22993,7 +22979,7 @@
         <v>1068</v>
       </c>
       <c r="D326" s="27" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="F326" s="3">
         <v>10</v>
@@ -23028,7 +23014,7 @@
         <v>1069</v>
       </c>
       <c r="D327" s="27" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
       <c r="E327" s="3">
         <v>103</v>
@@ -23066,7 +23052,7 @@
         <v>1070</v>
       </c>
       <c r="D328" s="27" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="F328" s="3">
         <v>10</v>
@@ -23101,7 +23087,7 @@
         <v>1071</v>
       </c>
       <c r="D329" s="27" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="F329" s="3">
         <v>10</v>
@@ -23136,7 +23122,7 @@
         <v>1072</v>
       </c>
       <c r="D330" s="27" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="E330" s="3">
         <v>103</v>
@@ -23174,7 +23160,7 @@
         <v>1073</v>
       </c>
       <c r="D331" s="27" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="F331" s="3">
         <v>10</v>
@@ -23209,7 +23195,7 @@
         <v>1074</v>
       </c>
       <c r="D332" s="27" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="F332" s="3">
         <v>10</v>
@@ -23244,7 +23230,7 @@
         <v>1075</v>
       </c>
       <c r="D333" s="27" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="E333" s="3">
         <v>103</v>
@@ -23282,7 +23268,7 @@
         <v>1076</v>
       </c>
       <c r="D334" s="27" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="F334" s="3">
         <v>10</v>
@@ -23317,7 +23303,7 @@
         <v>1077</v>
       </c>
       <c r="D335" s="27" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="F335" s="3">
         <v>10</v>
@@ -23352,7 +23338,7 @@
         <v>1078</v>
       </c>
       <c r="D336" s="27" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="E336" s="3">
         <v>103</v>
@@ -23390,7 +23376,7 @@
         <v>1079</v>
       </c>
       <c r="D337" s="27" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="F337" s="3">
         <v>10</v>
@@ -23425,7 +23411,7 @@
         <v>1080</v>
       </c>
       <c r="D338" s="27" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="F338" s="3">
         <v>10</v>
@@ -23460,7 +23446,7 @@
         <v>1081</v>
       </c>
       <c r="D339" s="27" t="s">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="E339" s="3">
         <v>103</v>
@@ -23498,7 +23484,7 @@
         <v>1082</v>
       </c>
       <c r="D340" s="27" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="F340" s="3">
         <v>10</v>
@@ -23533,7 +23519,7 @@
         <v>1083</v>
       </c>
       <c r="D341" s="27" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="F341" s="3">
         <v>10</v>
@@ -23568,7 +23554,7 @@
         <v>1084</v>
       </c>
       <c r="D342" s="27" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="E342" s="3">
         <v>103</v>
@@ -23606,7 +23592,7 @@
         <v>1085</v>
       </c>
       <c r="D343" s="27" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="F343" s="3">
         <v>10</v>
@@ -23641,7 +23627,7 @@
         <v>1086</v>
       </c>
       <c r="D344" s="27" t="s">
-        <v>1500</v>
+        <v>1499</v>
       </c>
       <c r="F344" s="3">
         <v>10</v>
@@ -23676,7 +23662,7 @@
         <v>1087</v>
       </c>
       <c r="D345" s="27" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="E345" s="3">
         <v>103</v>
@@ -23714,7 +23700,7 @@
         <v>1088</v>
       </c>
       <c r="D346" s="27" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="F346" s="3">
         <v>10</v>
@@ -23749,7 +23735,7 @@
         <v>1089</v>
       </c>
       <c r="D347" s="27" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="F347" s="3">
         <v>10</v>
@@ -23784,7 +23770,7 @@
         <v>1090</v>
       </c>
       <c r="D348" s="27" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="E348" s="3">
         <v>103</v>
@@ -23822,7 +23808,7 @@
         <v>1091</v>
       </c>
       <c r="D349" s="27" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="F349" s="3">
         <v>10</v>
@@ -23857,7 +23843,7 @@
         <v>1092</v>
       </c>
       <c r="D350" s="27" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="F350" s="3">
         <v>10</v>
@@ -23892,7 +23878,7 @@
         <v>1093</v>
       </c>
       <c r="D351" s="27" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
       <c r="E351" s="3">
         <v>103</v>
@@ -23930,7 +23916,7 @@
         <v>1094</v>
       </c>
       <c r="D352" s="27" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
       <c r="F352" s="3">
         <v>10</v>
@@ -23965,7 +23951,7 @@
         <v>1095</v>
       </c>
       <c r="D353" s="27" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
       <c r="F353" s="3">
         <v>10</v>
@@ -24000,7 +23986,7 @@
         <v>1096</v>
       </c>
       <c r="D354" s="27" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="E354" s="3">
         <v>103</v>
@@ -24038,7 +24024,7 @@
         <v>1097</v>
       </c>
       <c r="D355" s="27" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="F355" s="3">
         <v>10</v>
@@ -24073,7 +24059,7 @@
         <v>1098</v>
       </c>
       <c r="D356" s="27" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="F356" s="3">
         <v>10</v>
@@ -24108,7 +24094,7 @@
         <v>1099</v>
       </c>
       <c r="D357" s="27" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="E357" s="3">
         <v>103</v>
@@ -24146,7 +24132,7 @@
         <v>1100</v>
       </c>
       <c r="D358" s="27" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="F358" s="3">
         <v>10</v>
@@ -24181,7 +24167,7 @@
         <v>1101</v>
       </c>
       <c r="D359" s="27" t="s">
-        <v>1515</v>
+        <v>1514</v>
       </c>
       <c r="F359" s="3">
         <v>10</v>
@@ -24216,7 +24202,7 @@
         <v>1102</v>
       </c>
       <c r="D360" s="27" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="E360" s="3">
         <v>103</v>
@@ -24254,7 +24240,7 @@
         <v>1103</v>
       </c>
       <c r="D361" s="27" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="F361" s="3">
         <v>10</v>
@@ -24289,7 +24275,7 @@
         <v>1104</v>
       </c>
       <c r="D362" s="27" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
       <c r="F362" s="3">
         <v>10</v>
@@ -24324,7 +24310,7 @@
         <v>1105</v>
       </c>
       <c r="D363" s="27" t="s">
-        <v>1519</v>
+        <v>1518</v>
       </c>
       <c r="E363" s="3">
         <v>103</v>
@@ -24362,7 +24348,7 @@
         <v>1106</v>
       </c>
       <c r="D364" s="27" t="s">
-        <v>1520</v>
+        <v>1519</v>
       </c>
       <c r="F364" s="3">
         <v>10</v>
@@ -24397,7 +24383,7 @@
         <v>1107</v>
       </c>
       <c r="D365" s="27" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
       <c r="F365" s="3">
         <v>10</v>
@@ -24432,7 +24418,7 @@
         <v>1108</v>
       </c>
       <c r="D366" s="27" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="E366" s="3">
         <v>103</v>
@@ -24505,7 +24491,7 @@
         <v>1110</v>
       </c>
       <c r="D368" s="27" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
       <c r="F368" s="3">
         <v>10</v>
@@ -24540,7 +24526,7 @@
         <v>1111</v>
       </c>
       <c r="D369" s="27" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
       <c r="E369" s="3">
         <v>103</v>
@@ -24578,7 +24564,7 @@
         <v>1112</v>
       </c>
       <c r="D370" s="27" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
       <c r="F370" s="3">
         <v>10</v>
@@ -24613,7 +24599,7 @@
         <v>1113</v>
       </c>
       <c r="D371" s="27" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="F371" s="3">
         <v>10</v>
@@ -24648,7 +24634,7 @@
         <v>1114</v>
       </c>
       <c r="D372" s="27" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="E372" s="3">
         <v>103</v>
@@ -24721,7 +24707,7 @@
         <v>1116</v>
       </c>
       <c r="D374" s="27" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
       <c r="F374" s="3">
         <v>10</v>
@@ -24756,7 +24742,7 @@
         <v>1117</v>
       </c>
       <c r="D375" s="27" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="E375" s="3">
         <v>103</v>
@@ -24794,7 +24780,7 @@
         <v>1118</v>
       </c>
       <c r="D376" s="27" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
       <c r="F376" s="3">
         <v>10</v>
@@ -24829,7 +24815,7 @@
         <v>1119</v>
       </c>
       <c r="D377" s="27" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="F377" s="3">
         <v>10</v>
@@ -24864,7 +24850,7 @@
         <v>1120</v>
       </c>
       <c r="D378" s="27" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="E378" s="3">
         <v>103</v>
@@ -24937,7 +24923,7 @@
         <v>1122</v>
       </c>
       <c r="D380" s="27" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="F380" s="3">
         <v>10</v>
@@ -24972,7 +24958,7 @@
         <v>1123</v>
       </c>
       <c r="D381" s="27" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
       <c r="E381" s="3">
         <v>103</v>
@@ -25010,7 +24996,7 @@
         <v>1124</v>
       </c>
       <c r="D382" s="27" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="F382" s="3">
         <v>10</v>
@@ -25045,7 +25031,7 @@
         <v>1125</v>
       </c>
       <c r="D383" s="27" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="F383" s="3">
         <v>10</v>
@@ -25080,7 +25066,7 @@
         <v>1126</v>
       </c>
       <c r="D384" s="27" t="s">
-        <v>1537</v>
+        <v>1536</v>
       </c>
       <c r="E384" s="3">
         <v>103</v>
@@ -25118,7 +25104,7 @@
         <v>1127</v>
       </c>
       <c r="D385" s="27" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
       <c r="F385" s="3">
         <v>10</v>
@@ -25153,7 +25139,7 @@
         <v>1128</v>
       </c>
       <c r="D386" s="27" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
       <c r="F386" s="3">
         <v>10</v>
@@ -25188,7 +25174,7 @@
         <v>1129</v>
       </c>
       <c r="D387" s="27" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
       <c r="E387" s="3">
         <v>103</v>
@@ -25261,7 +25247,7 @@
         <v>1131</v>
       </c>
       <c r="D389" s="27" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="F389" s="3">
         <v>10</v>
@@ -25296,7 +25282,7 @@
         <v>1132</v>
       </c>
       <c r="D390" s="27" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="E390" s="3">
         <v>103</v>
@@ -25334,7 +25320,7 @@
         <v>1133</v>
       </c>
       <c r="D391" s="27" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="F391" s="3">
         <v>10</v>
@@ -25369,7 +25355,7 @@
         <v>1134</v>
       </c>
       <c r="D392" s="27" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
       <c r="F392" s="3">
         <v>10</v>
@@ -25404,7 +25390,7 @@
         <v>1135</v>
       </c>
       <c r="D393" s="27" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="E393" s="3">
         <v>103</v>
@@ -25442,7 +25428,7 @@
         <v>1136</v>
       </c>
       <c r="D394" s="27" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="F394" s="3">
         <v>10</v>
@@ -25477,7 +25463,7 @@
         <v>1137</v>
       </c>
       <c r="D395" s="27" t="s">
-        <v>1547</v>
+        <v>1546</v>
       </c>
       <c r="F395" s="3">
         <v>10</v>
@@ -25512,7 +25498,7 @@
         <v>1138</v>
       </c>
       <c r="D396" s="27" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="E396" s="3">
         <v>103</v>
@@ -25585,7 +25571,7 @@
         <v>1140</v>
       </c>
       <c r="D398" s="27" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
       <c r="F398" s="3">
         <v>10</v>
@@ -25620,7 +25606,7 @@
         <v>1141</v>
       </c>
       <c r="D399" s="27" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="E399" s="3">
         <v>103</v>
@@ -25658,7 +25644,7 @@
         <v>1142</v>
       </c>
       <c r="D400" s="27" t="s">
-        <v>1551</v>
+        <v>1550</v>
       </c>
       <c r="F400" s="3">
         <v>10</v>
@@ -25693,7 +25679,7 @@
         <v>1143</v>
       </c>
       <c r="D401" s="27" t="s">
-        <v>1552</v>
+        <v>1551</v>
       </c>
       <c r="F401" s="3">
         <v>10</v>
@@ -25728,7 +25714,7 @@
         <v>1144</v>
       </c>
       <c r="D402" s="27" t="s">
-        <v>1553</v>
+        <v>1552</v>
       </c>
       <c r="E402" s="3">
         <v>103</v>
@@ -25766,7 +25752,7 @@
         <v>1145</v>
       </c>
       <c r="D403" s="27" t="s">
-        <v>1554</v>
+        <v>1553</v>
       </c>
       <c r="F403" s="3">
         <v>10</v>
@@ -25801,7 +25787,7 @@
         <v>1146</v>
       </c>
       <c r="D404" s="27" t="s">
-        <v>1555</v>
+        <v>1554</v>
       </c>
       <c r="F404" s="3">
         <v>10</v>
@@ -25836,7 +25822,7 @@
         <v>1147</v>
       </c>
       <c r="D405" s="27" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="E405" s="3">
         <v>103</v>
@@ -25874,7 +25860,7 @@
         <v>1148</v>
       </c>
       <c r="D406" s="27" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="F406" s="3">
         <v>10</v>
@@ -25909,7 +25895,7 @@
         <v>1149</v>
       </c>
       <c r="D407" s="27" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="F407" s="3">
         <v>10</v>
@@ -25944,7 +25930,7 @@
         <v>1150</v>
       </c>
       <c r="D408" s="27" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="E408" s="3">
         <v>103</v>
@@ -25982,7 +25968,7 @@
         <v>1151</v>
       </c>
       <c r="D409" s="27" t="s">
-        <v>1560</v>
+        <v>1559</v>
       </c>
       <c r="F409" s="3">
         <v>10</v>
@@ -26017,7 +26003,7 @@
         <v>1152</v>
       </c>
       <c r="D410" s="27" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
       <c r="F410" s="3">
         <v>10</v>
@@ -26052,7 +26038,7 @@
         <v>1153</v>
       </c>
       <c r="D411" s="27" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="E411" s="3">
         <v>103</v>
@@ -26090,7 +26076,7 @@
         <v>1154</v>
       </c>
       <c r="D412" s="27" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="F412" s="3">
         <v>10</v>
@@ -26125,7 +26111,7 @@
         <v>1155</v>
       </c>
       <c r="D413" s="27" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="F413" s="3">
         <v>10</v>
@@ -26160,7 +26146,7 @@
         <v>1156</v>
       </c>
       <c r="D414" s="27" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="E414" s="3">
         <v>103</v>
@@ -26198,7 +26184,7 @@
         <v>1157</v>
       </c>
       <c r="D415" s="27" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="F415" s="3">
         <v>10</v>
@@ -26233,7 +26219,7 @@
         <v>1158</v>
       </c>
       <c r="D416" s="27" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="F416" s="3">
         <v>10</v>
@@ -26268,7 +26254,7 @@
         <v>1159</v>
       </c>
       <c r="D417" s="27" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
       <c r="E417" s="3">
         <v>103</v>
@@ -26306,7 +26292,7 @@
         <v>1160</v>
       </c>
       <c r="D418" s="27" t="s">
-        <v>1569</v>
+        <v>1568</v>
       </c>
       <c r="F418" s="3">
         <v>10</v>
@@ -26341,7 +26327,7 @@
         <v>1161</v>
       </c>
       <c r="D419" s="27" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
       <c r="F419" s="3">
         <v>10</v>
@@ -26376,7 +26362,7 @@
         <v>1162</v>
       </c>
       <c r="D420" s="27" t="s">
-        <v>1571</v>
+        <v>1570</v>
       </c>
       <c r="E420" s="3">
         <v>103</v>
@@ -26414,7 +26400,7 @@
         <v>1163</v>
       </c>
       <c r="D421" s="27" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="F421" s="3">
         <v>10</v>
@@ -26449,7 +26435,7 @@
         <v>1164</v>
       </c>
       <c r="D422" s="27" t="s">
-        <v>1573</v>
+        <v>1572</v>
       </c>
       <c r="F422" s="3">
         <v>10</v>
@@ -26484,7 +26470,7 @@
         <v>1165</v>
       </c>
       <c r="D423" s="27" t="s">
-        <v>1574</v>
+        <v>1573</v>
       </c>
       <c r="E423" s="3">
         <v>103</v>
@@ -26522,7 +26508,7 @@
         <v>1166</v>
       </c>
       <c r="D424" s="27" t="s">
-        <v>1575</v>
+        <v>1574</v>
       </c>
       <c r="F424" s="3">
         <v>10</v>
@@ -26557,7 +26543,7 @@
         <v>1167</v>
       </c>
       <c r="D425" s="27" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
       <c r="F425" s="3">
         <v>10</v>
@@ -26592,7 +26578,7 @@
         <v>1168</v>
       </c>
       <c r="D426" s="27" t="s">
-        <v>1577</v>
+        <v>1576</v>
       </c>
       <c r="E426" s="3">
         <v>103</v>
@@ -26630,7 +26616,7 @@
         <v>1169</v>
       </c>
       <c r="D427" s="27" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="F427" s="3">
         <v>10</v>
@@ -26665,7 +26651,7 @@
         <v>1170</v>
       </c>
       <c r="D428" s="27" t="s">
-        <v>1579</v>
+        <v>1578</v>
       </c>
       <c r="F428" s="3">
         <v>10</v>
@@ -26700,7 +26686,7 @@
         <v>1171</v>
       </c>
       <c r="D429" s="27" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="E429" s="3">
         <v>103</v>
@@ -26738,7 +26724,7 @@
         <v>1172</v>
       </c>
       <c r="D430" s="27" t="s">
-        <v>1581</v>
+        <v>1580</v>
       </c>
       <c r="F430" s="3">
         <v>10</v>
@@ -26773,7 +26759,7 @@
         <v>1173</v>
       </c>
       <c r="D431" s="27" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="F431" s="3">
         <v>10</v>
@@ -26808,7 +26794,7 @@
         <v>1174</v>
       </c>
       <c r="D432" s="27" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="E432" s="3">
         <v>103</v>
@@ -26846,7 +26832,7 @@
         <v>1175</v>
       </c>
       <c r="D433" s="27" t="s">
-        <v>1584</v>
+        <v>1583</v>
       </c>
       <c r="F433" s="3">
         <v>10</v>
@@ -26881,7 +26867,7 @@
         <v>1176</v>
       </c>
       <c r="D434" s="27" t="s">
-        <v>1585</v>
+        <v>1584</v>
       </c>
       <c r="F434" s="3">
         <v>10</v>
@@ -26916,7 +26902,7 @@
         <v>1177</v>
       </c>
       <c r="D435" s="27" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="E435" s="3">
         <v>103</v>
@@ -26954,7 +26940,7 @@
         <v>1178</v>
       </c>
       <c r="D436" s="27" t="s">
-        <v>1587</v>
+        <v>1586</v>
       </c>
       <c r="F436" s="3">
         <v>10</v>
@@ -26989,7 +26975,7 @@
         <v>1179</v>
       </c>
       <c r="D437" s="27" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="F437" s="3">
         <v>10</v>
@@ -27024,7 +27010,7 @@
         <v>1180</v>
       </c>
       <c r="D438" s="27" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="E438" s="3">
         <v>103</v>
@@ -27062,7 +27048,7 @@
         <v>1181</v>
       </c>
       <c r="D439" s="27" t="s">
-        <v>1590</v>
+        <v>1589</v>
       </c>
       <c r="F439" s="3">
         <v>10</v>
@@ -27097,7 +27083,7 @@
         <v>1182</v>
       </c>
       <c r="D440" s="27" t="s">
-        <v>1591</v>
+        <v>1590</v>
       </c>
       <c r="F440" s="3">
         <v>10</v>
@@ -27132,7 +27118,7 @@
         <v>1183</v>
       </c>
       <c r="D441" s="27" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
       <c r="E441" s="3">
         <v>103</v>
@@ -27170,7 +27156,7 @@
         <v>1184</v>
       </c>
       <c r="D442" s="27" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
       <c r="F442" s="3">
         <v>10</v>
@@ -27205,7 +27191,7 @@
         <v>1185</v>
       </c>
       <c r="D443" s="27" t="s">
-        <v>1594</v>
+        <v>1593</v>
       </c>
       <c r="F443" s="3">
         <v>10</v>
@@ -27240,7 +27226,7 @@
         <v>1186</v>
       </c>
       <c r="D444" s="27" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="E444" s="3">
         <v>103</v>
@@ -27278,7 +27264,7 @@
         <v>1187</v>
       </c>
       <c r="D445" s="27" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
       <c r="F445" s="3">
         <v>10</v>
@@ -27313,7 +27299,7 @@
         <v>1188</v>
       </c>
       <c r="D446" s="27" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
       <c r="F446" s="3">
         <v>10</v>
@@ -27348,7 +27334,7 @@
         <v>1189</v>
       </c>
       <c r="D447" s="27" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
       <c r="E447" s="3">
         <v>103</v>
@@ -27386,7 +27372,7 @@
         <v>1190</v>
       </c>
       <c r="D448" s="27" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="F448" s="3">
         <v>10</v>
@@ -27421,7 +27407,7 @@
         <v>1191</v>
       </c>
       <c r="D449" s="27" t="s">
-        <v>1600</v>
+        <v>1599</v>
       </c>
       <c r="F449" s="3">
         <v>10</v>
@@ -27456,7 +27442,7 @@
         <v>1192</v>
       </c>
       <c r="D450" s="27" t="s">
-        <v>1601</v>
+        <v>1600</v>
       </c>
       <c r="E450" s="3">
         <v>103</v>
@@ -27494,7 +27480,7 @@
         <v>1193</v>
       </c>
       <c r="D451" s="27" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
       <c r="F451" s="3">
         <v>10</v>
@@ -27529,7 +27515,7 @@
         <v>1194</v>
       </c>
       <c r="D452" s="27" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="F452" s="3">
         <v>10</v>
@@ -27564,7 +27550,7 @@
         <v>1195</v>
       </c>
       <c r="D453" s="27" t="s">
-        <v>1604</v>
+        <v>1603</v>
       </c>
       <c r="E453" s="3">
         <v>103</v>
@@ -27602,7 +27588,7 @@
         <v>1196</v>
       </c>
       <c r="D454" s="27" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="F454" s="3">
         <v>10</v>
@@ -27637,7 +27623,7 @@
         <v>1197</v>
       </c>
       <c r="D455" s="27" t="s">
-        <v>1606</v>
+        <v>1605</v>
       </c>
       <c r="F455" s="3">
         <v>10</v>
@@ -27672,7 +27658,7 @@
         <v>1198</v>
       </c>
       <c r="D456" s="27" t="s">
-        <v>1607</v>
+        <v>1606</v>
       </c>
       <c r="E456" s="3">
         <v>103</v>
@@ -27710,7 +27696,7 @@
         <v>1199</v>
       </c>
       <c r="D457" s="27" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="F457" s="3">
         <v>10</v>
@@ -28041,7 +28027,7 @@
         <v>314</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>661</v>
@@ -28130,7 +28116,7 @@
         <v>298</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>660</v>
@@ -39888,7 +39874,7 @@
       </c>
       <c r="AC205" s="24"/>
       <c r="AD205" s="24" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="AH205" s="6"/>
       <c r="AI205" s="3"/>
@@ -43425,7 +43411,7 @@
       </c>
       <c r="AC266" s="24"/>
       <c r="AD266" s="24" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="AH266" s="6"/>
       <c r="AI266" s="3"/>
@@ -44074,8 +44060,8 @@
       </c>
       <c r="Q277" s="26"/>
       <c r="R277" s="26"/>
-      <c r="Z277" s="26" t="s">
-        <v>1361</v>
+      <c r="Z277" s="26">
+        <v>25084011</v>
       </c>
       <c r="AC277" s="24"/>
       <c r="AD277" s="24" t="s">
@@ -44124,8 +44110,8 @@
       </c>
       <c r="Q278" s="26"/>
       <c r="R278" s="26"/>
-      <c r="Z278" s="26" t="s">
-        <v>1361</v>
+      <c r="Z278" s="26">
+        <v>25084011</v>
       </c>
       <c r="AC278" s="24"/>
       <c r="AD278" s="24" t="s">
@@ -44189,8 +44175,8 @@
       <c r="Z279" s="26">
         <v>25084016</v>
       </c>
-      <c r="AA279" s="26" t="s">
-        <v>1361</v>
+      <c r="AA279" s="26">
+        <v>25084011</v>
       </c>
       <c r="AC279" s="24"/>
       <c r="AD279" s="24" t="s">
@@ -44251,8 +44237,8 @@
       <c r="Z280" s="26">
         <v>25084016</v>
       </c>
-      <c r="AA280" s="26" t="s">
-        <v>1361</v>
+      <c r="AA280" s="26">
+        <v>25084011</v>
       </c>
       <c r="AC280" s="24"/>
       <c r="AD280" s="24" t="s">
@@ -45787,7 +45773,7 @@
       </c>
       <c r="AC307" s="24"/>
       <c r="AD307" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="308" spans="2:35" ht="17.25" x14ac:dyDescent="0.3">
@@ -45846,7 +45832,7 @@
       </c>
       <c r="AC308" s="24"/>
       <c r="AD308" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="309" spans="2:35" ht="17.25" x14ac:dyDescent="0.3">
@@ -46934,7 +46920,7 @@
       </c>
       <c r="AC327" s="24"/>
       <c r="AD327" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="AH327" s="6"/>
       <c r="AI327" s="3"/>
@@ -46998,7 +46984,7 @@
       </c>
       <c r="AC328" s="24"/>
       <c r="AD328" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="AH328" s="6"/>
       <c r="AI328" s="3"/>
@@ -47282,7 +47268,7 @@
       </c>
       <c r="AC333" s="24"/>
       <c r="AD333" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="AH333" s="6"/>
       <c r="AI333" s="3"/>
@@ -47335,7 +47321,7 @@
       </c>
       <c r="AC334" s="24"/>
       <c r="AD334" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="AH334" s="6"/>
       <c r="AI334" s="3"/>
@@ -47391,7 +47377,7 @@
       </c>
       <c r="AC335" s="24"/>
       <c r="AD335" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="AH335" s="6"/>
       <c r="AI335" s="3"/>
@@ -47444,7 +47430,7 @@
       </c>
       <c r="AC336" s="24"/>
       <c r="AD336" t="s">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="AH336" s="6"/>
       <c r="AI336" s="3"/>
@@ -47932,7 +47918,7 @@
       </c>
       <c r="AC344" s="24"/>
       <c r="AD344" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="AH344" s="6"/>
       <c r="AI344" s="3"/>
@@ -48315,7 +48301,7 @@
       </c>
       <c r="AC351" s="24"/>
       <c r="AD351" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="AH351" s="6"/>
       <c r="AI351" s="3"/>
@@ -48368,7 +48354,7 @@
       </c>
       <c r="AC352" s="24"/>
       <c r="AD352" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="AH352" s="6"/>
       <c r="AI352" s="3"/>
@@ -49235,7 +49221,7 @@
         <v>316</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>315</v>
@@ -49244,7 +49230,7 @@
         <v>1202</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="H1" s="26" t="s">
         <v>1308</v>
@@ -49279,7 +49265,7 @@
         <v>300</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>299</v>
@@ -49288,7 +49274,7 @@
         <v>1203</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="H2" s="26" t="s">
         <v>1343</v>
@@ -49400,7 +49386,7 @@
         <v>5</v>
       </c>
       <c r="O5" s="29" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.2">
@@ -49435,7 +49421,7 @@
         <v>8</v>
       </c>
       <c r="O6" s="29" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.2">
@@ -49470,7 +49456,7 @@
         <v>3</v>
       </c>
       <c r="O7" s="29" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.2">
@@ -49613,7 +49599,7 @@
         <v>200</v>
       </c>
       <c r="O11" s="29" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.2">
@@ -49890,7 +49876,7 @@
         <v>500</v>
       </c>
       <c r="O19" s="29" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="20" spans="2:15" x14ac:dyDescent="0.2">
@@ -50088,7 +50074,7 @@
         <v>1307</v>
       </c>
       <c r="O25" s="29" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="26" spans="2:15" x14ac:dyDescent="0.2">
@@ -53392,10 +53378,10 @@
         <v>25084101</v>
       </c>
       <c r="F5" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="G5" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -53409,10 +53395,10 @@
         <v>25084102</v>
       </c>
       <c r="F6" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="G6" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -53426,10 +53412,10 @@
         <v>25084103</v>
       </c>
       <c r="F7" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="G7" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -53443,10 +53429,10 @@
         <v>25084104</v>
       </c>
       <c r="F8" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="G8" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -53460,10 +53446,10 @@
         <v>25084105</v>
       </c>
       <c r="F9" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="G9" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -53477,10 +53463,10 @@
         <v>25084106</v>
       </c>
       <c r="F10" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="G10" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -53494,10 +53480,10 @@
         <v>25084107</v>
       </c>
       <c r="F11" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="G11" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -53511,10 +53497,10 @@
         <v>25084108</v>
       </c>
       <c r="F12" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="G12" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -53528,10 +53514,10 @@
         <v>25084109</v>
       </c>
       <c r="F13" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="G13" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -53545,10 +53531,10 @@
         <v>25084110</v>
       </c>
       <c r="F14" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="G14" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -53562,10 +53548,10 @@
         <v>25084111</v>
       </c>
       <c r="F15" t="s">
+        <v>1423</v>
+      </c>
+      <c r="G15" t="s">
         <v>1424</v>
-      </c>
-      <c r="G15" t="s">
-        <v>1425</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -53579,10 +53565,10 @@
         <v>25084112</v>
       </c>
       <c r="F16" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="G16" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
@@ -53596,10 +53582,10 @@
         <v>25084113</v>
       </c>
       <c r="F17" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="G17" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
@@ -53613,10 +53599,10 @@
         <v>25084114</v>
       </c>
       <c r="F18" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="G18" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
@@ -53630,10 +53616,10 @@
         <v>25084115</v>
       </c>
       <c r="F19" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="G19" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
@@ -53647,10 +53633,10 @@
         <v>25084116</v>
       </c>
       <c r="F20" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
       <c r="G20" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.25">
@@ -53664,10 +53650,10 @@
         <v>25084117</v>
       </c>
       <c r="F21" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
       <c r="G21" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.25">
@@ -53681,10 +53667,10 @@
         <v>25084118</v>
       </c>
       <c r="F22" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="G22" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.25">
@@ -53698,10 +53684,10 @@
         <v>25084119</v>
       </c>
       <c r="F23" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="G23" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.25">
@@ -53715,10 +53701,10 @@
         <v>25084120</v>
       </c>
       <c r="F24" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
       <c r="G24" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.25">
@@ -53732,10 +53718,10 @@
         <v>25084121</v>
       </c>
       <c r="F25" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="G25" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
@@ -53749,10 +53735,10 @@
         <v>25084122</v>
       </c>
       <c r="F26" s="22" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="G26" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="27" spans="2:7" x14ac:dyDescent="0.2">
@@ -53766,10 +53752,10 @@
         <v>25084123</v>
       </c>
       <c r="F27" s="22" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
       <c r="G27" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.25">
@@ -53783,10 +53769,10 @@
         <v>25084124</v>
       </c>
       <c r="F28" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="G28" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="29" spans="2:7" x14ac:dyDescent="0.25">
@@ -53800,10 +53786,10 @@
         <v>25084125</v>
       </c>
       <c r="F29" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="G29" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
     </row>
   </sheetData>

--- a/source/bin/excel/amulet.xlsx
+++ b/source/bin/excel/amulet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Work\Git\liqi-excel\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\liqi-excel\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40A55AAB-298C-451E-973F-E54DFFA8674C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B20446D-42D7-4176-9281-D201A26E5421}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="28110" windowHeight="16440" activeTab="2" xr2:uid="{DC9447C4-71D8-6D42-B8C0-4F33987E6336}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{DC9447C4-71D8-6D42-B8C0-4F33987E6336}"/>
   </bookViews>
   <sheets>
     <sheet name="export" sheetId="2" r:id="rId1"/>
@@ -30,10 +30,19 @@
     <sheet name="amulet_task" sheetId="13" r:id="rId15"/>
     <sheet name="amulet_large_number" sheetId="17" r:id="rId16"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -78,7 +87,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2476" uniqueCount="1637">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2492" uniqueCount="1653">
   <si>
     <t>group</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -5371,6 +5380,70 @@
   </si>
   <si>
     <t>大数单位</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1000000000000</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>100000000000</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>10000000000000</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>100000000000000</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>500000000000000</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>4000000000000000</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>20000000000000000</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>160000000000000000</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>800000000000000000</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>6400000000000000000</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>32000000000000000000</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>256000000000000000000</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>100354000000</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1355020000000</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>20565900000000</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>348311510000000</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -5598,7 +5671,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -5684,7 +5757,14 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="11" fontId="3" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -11690,7 +11770,7 @@
       <c r="C5" s="3">
         <v>101</v>
       </c>
-      <c r="D5" s="25">
+      <c r="D5" s="43">
         <v>350</v>
       </c>
       <c r="F5" s="3">
@@ -11716,7 +11796,7 @@
       <c r="C6" s="3">
         <v>102</v>
       </c>
-      <c r="D6" s="25">
+      <c r="D6" s="43">
         <v>700</v>
       </c>
       <c r="F6" s="3">
@@ -11742,7 +11822,7 @@
       <c r="C7" s="3">
         <v>103</v>
       </c>
-      <c r="D7" s="25">
+      <c r="D7" s="43">
         <v>1000</v>
       </c>
       <c r="F7" s="3">
@@ -11774,7 +11854,7 @@
       <c r="C8" s="3">
         <v>201</v>
       </c>
-      <c r="D8" s="25">
+      <c r="D8" s="43">
         <v>1500</v>
       </c>
       <c r="F8" s="3">
@@ -11800,7 +11880,7 @@
       <c r="C9" s="3">
         <v>202</v>
       </c>
-      <c r="D9" s="25">
+      <c r="D9" s="43">
         <v>2400</v>
       </c>
       <c r="F9" s="3">
@@ -11826,7 +11906,7 @@
       <c r="C10" s="3">
         <v>203</v>
       </c>
-      <c r="D10" s="25">
+      <c r="D10" s="43">
         <v>3600</v>
       </c>
       <c r="F10" s="3">
@@ -11858,7 +11938,7 @@
       <c r="C11" s="3">
         <v>301</v>
       </c>
-      <c r="D11" s="25">
+      <c r="D11" s="43">
         <v>5000</v>
       </c>
       <c r="F11" s="3">
@@ -11884,7 +11964,7 @@
       <c r="C12" s="3">
         <v>302</v>
       </c>
-      <c r="D12" s="25">
+      <c r="D12" s="43">
         <v>7500</v>
       </c>
       <c r="F12" s="3">
@@ -11910,7 +11990,7 @@
       <c r="C13" s="3">
         <v>303</v>
       </c>
-      <c r="D13" s="25">
+      <c r="D13" s="43">
         <v>10000</v>
       </c>
       <c r="F13" s="3">
@@ -11942,7 +12022,7 @@
       <c r="C14" s="3">
         <v>401</v>
       </c>
-      <c r="D14" s="25">
+      <c r="D14" s="43">
         <v>13000</v>
       </c>
       <c r="F14" s="3">
@@ -11968,7 +12048,7 @@
       <c r="C15" s="3">
         <v>402</v>
       </c>
-      <c r="D15" s="25">
+      <c r="D15" s="43">
         <v>19000</v>
       </c>
       <c r="F15" s="3">
@@ -11994,7 +12074,7 @@
       <c r="C16" s="3">
         <v>403</v>
       </c>
-      <c r="D16" s="25">
+      <c r="D16" s="43">
         <v>25000</v>
       </c>
       <c r="F16" s="3">
@@ -12026,7 +12106,7 @@
       <c r="C17" s="3">
         <v>501</v>
       </c>
-      <c r="D17" s="25">
+      <c r="D17" s="43">
         <v>35000</v>
       </c>
       <c r="F17" s="3">
@@ -12052,7 +12132,7 @@
       <c r="C18" s="3">
         <v>502</v>
       </c>
-      <c r="D18" s="25">
+      <c r="D18" s="43">
         <v>50000</v>
       </c>
       <c r="F18" s="3">
@@ -12078,7 +12158,7 @@
       <c r="C19" s="3">
         <v>503</v>
       </c>
-      <c r="D19" s="25">
+      <c r="D19" s="43">
         <v>88888</v>
       </c>
       <c r="F19" s="3">
@@ -12113,7 +12193,7 @@
       <c r="C20" s="3">
         <v>1001</v>
       </c>
-      <c r="D20" s="25">
+      <c r="D20" s="43">
         <v>100000</v>
       </c>
       <c r="F20" s="3">
@@ -12145,7 +12225,7 @@
       <c r="C21" s="3">
         <v>1002</v>
       </c>
-      <c r="D21" s="25">
+      <c r="D21" s="43">
         <v>150000</v>
       </c>
       <c r="F21" s="3">
@@ -12177,7 +12257,7 @@
       <c r="C22" s="3">
         <v>1003</v>
       </c>
-      <c r="D22" s="25">
+      <c r="D22" s="43">
         <v>200000</v>
       </c>
       <c r="F22" s="3">
@@ -12209,7 +12289,7 @@
       <c r="C23" s="3">
         <v>1004</v>
       </c>
-      <c r="D23" s="25">
+      <c r="D23" s="43">
         <v>250000</v>
       </c>
       <c r="F23" s="3">
@@ -12241,7 +12321,7 @@
       <c r="C24" s="3">
         <v>1005</v>
       </c>
-      <c r="D24" s="25">
+      <c r="D24" s="43">
         <v>300000</v>
       </c>
       <c r="F24" s="3">
@@ -12273,7 +12353,7 @@
       <c r="C25" s="3">
         <v>1006</v>
       </c>
-      <c r="D25" s="25">
+      <c r="D25" s="43">
         <v>400000</v>
       </c>
       <c r="F25" s="3">
@@ -12305,7 +12385,7 @@
       <c r="C26" s="3">
         <v>1007</v>
       </c>
-      <c r="D26" s="25">
+      <c r="D26" s="43">
         <v>500000</v>
       </c>
       <c r="F26" s="3">
@@ -12337,7 +12417,7 @@
       <c r="C27" s="3">
         <v>1008</v>
       </c>
-      <c r="D27" s="25">
+      <c r="D27" s="43">
         <v>600000</v>
       </c>
       <c r="F27" s="3">
@@ -12369,7 +12449,7 @@
       <c r="C28" s="3">
         <v>1009</v>
       </c>
-      <c r="D28" s="25">
+      <c r="D28" s="43">
         <v>800000</v>
       </c>
       <c r="F28" s="3">
@@ -12401,7 +12481,7 @@
       <c r="C29" s="3">
         <v>1010</v>
       </c>
-      <c r="D29" s="25">
+      <c r="D29" s="43">
         <v>1000000</v>
       </c>
       <c r="F29" s="3">
@@ -12430,7 +12510,7 @@
       <c r="C30" s="3">
         <v>101</v>
       </c>
-      <c r="D30" s="25">
+      <c r="D30" s="43">
         <v>200</v>
       </c>
       <c r="E30" s="21"/>
@@ -12460,7 +12540,7 @@
       <c r="C31" s="3">
         <v>102</v>
       </c>
-      <c r="D31" s="25">
+      <c r="D31" s="43">
         <v>400</v>
       </c>
       <c r="E31" s="21"/>
@@ -12490,7 +12570,7 @@
       <c r="C32" s="3">
         <v>103</v>
       </c>
-      <c r="D32" s="25">
+      <c r="D32" s="43">
         <v>700</v>
       </c>
       <c r="E32" s="3">
@@ -12528,7 +12608,7 @@
       <c r="C33" s="3">
         <v>201</v>
       </c>
-      <c r="D33" s="25">
+      <c r="D33" s="43">
         <v>1000</v>
       </c>
       <c r="F33" s="3">
@@ -12557,7 +12637,7 @@
       <c r="C34" s="3">
         <v>202</v>
       </c>
-      <c r="D34" s="25">
+      <c r="D34" s="43">
         <v>1500</v>
       </c>
       <c r="F34" s="3">
@@ -12586,7 +12666,7 @@
       <c r="C35" s="3">
         <v>203</v>
       </c>
-      <c r="D35" s="25">
+      <c r="D35" s="43">
         <v>2100</v>
       </c>
       <c r="E35" s="3">
@@ -12624,7 +12704,7 @@
       <c r="C36" s="3">
         <v>301</v>
       </c>
-      <c r="D36" s="25">
+      <c r="D36" s="43">
         <v>3000</v>
       </c>
       <c r="F36" s="3">
@@ -12653,7 +12733,7 @@
       <c r="C37" s="3">
         <v>302</v>
       </c>
-      <c r="D37" s="25">
+      <c r="D37" s="43">
         <v>4000</v>
       </c>
       <c r="F37" s="3">
@@ -12682,7 +12762,7 @@
       <c r="C38" s="3">
         <v>303</v>
       </c>
-      <c r="D38" s="25">
+      <c r="D38" s="43">
         <v>5200</v>
       </c>
       <c r="E38" s="3">
@@ -12720,7 +12800,7 @@
       <c r="C39" s="3">
         <v>401</v>
       </c>
-      <c r="D39" s="25">
+      <c r="D39" s="43">
         <v>7000</v>
       </c>
       <c r="F39" s="3">
@@ -12749,7 +12829,7 @@
       <c r="C40" s="3">
         <v>402</v>
       </c>
-      <c r="D40" s="25">
+      <c r="D40" s="43">
         <v>9800</v>
       </c>
       <c r="F40" s="3">
@@ -12778,7 +12858,7 @@
       <c r="C41" s="3">
         <v>403</v>
       </c>
-      <c r="D41" s="25">
+      <c r="D41" s="43">
         <v>15000</v>
       </c>
       <c r="E41" s="3">
@@ -12816,7 +12896,7 @@
       <c r="C42" s="3">
         <v>501</v>
       </c>
-      <c r="D42" s="25">
+      <c r="D42" s="43">
         <v>22500</v>
       </c>
       <c r="F42" s="3">
@@ -12845,7 +12925,7 @@
       <c r="C43" s="3">
         <v>502</v>
       </c>
-      <c r="D43" s="25">
+      <c r="D43" s="43">
         <v>33300</v>
       </c>
       <c r="F43" s="3">
@@ -12874,7 +12954,7 @@
       <c r="C44" s="3">
         <v>503</v>
       </c>
-      <c r="D44" s="25">
+      <c r="D44" s="43">
         <v>50000</v>
       </c>
       <c r="E44" s="3">
@@ -12915,7 +12995,7 @@
       <c r="C45" s="3">
         <v>1001</v>
       </c>
-      <c r="D45" s="25">
+      <c r="D45" s="43">
         <v>1000000</v>
       </c>
       <c r="F45" s="3">
@@ -12950,7 +13030,7 @@
       <c r="C46" s="3">
         <v>1002</v>
       </c>
-      <c r="D46" s="25">
+      <c r="D46" s="43">
         <v>10000000</v>
       </c>
       <c r="F46" s="3">
@@ -12985,7 +13065,7 @@
       <c r="C47" s="3">
         <v>1003</v>
       </c>
-      <c r="D47" s="25">
+      <c r="D47" s="43">
         <v>100000000</v>
       </c>
       <c r="E47" s="3">
@@ -13023,7 +13103,7 @@
       <c r="C48" s="3">
         <v>1004</v>
       </c>
-      <c r="D48" s="25">
+      <c r="D48" s="43">
         <v>1000000000</v>
       </c>
       <c r="F48" s="3">
@@ -13058,7 +13138,7 @@
       <c r="C49" s="3">
         <v>1005</v>
       </c>
-      <c r="D49" s="25">
+      <c r="D49" s="43">
         <v>10000000000</v>
       </c>
       <c r="F49" s="3">
@@ -13093,8 +13173,8 @@
       <c r="C50" s="3">
         <v>1006</v>
       </c>
-      <c r="D50" s="43">
-        <v>100000000000</v>
+      <c r="D50" s="44" t="s">
+        <v>1638</v>
       </c>
       <c r="E50" s="3">
         <v>103</v>
@@ -13131,8 +13211,8 @@
       <c r="C51" s="3">
         <v>1007</v>
       </c>
-      <c r="D51" s="43">
-        <v>1000000000000</v>
+      <c r="D51" s="45" t="s">
+        <v>1637</v>
       </c>
       <c r="F51" s="3">
         <v>10</v>
@@ -13166,8 +13246,8 @@
       <c r="C52" s="3">
         <v>1008</v>
       </c>
-      <c r="D52" s="43">
-        <v>10000000000000</v>
+      <c r="D52" s="45" t="s">
+        <v>1639</v>
       </c>
       <c r="F52" s="3">
         <v>10</v>
@@ -13201,8 +13281,8 @@
       <c r="C53" s="3">
         <v>1009</v>
       </c>
-      <c r="D53" s="43">
-        <v>100000000000000</v>
+      <c r="D53" s="45" t="s">
+        <v>1640</v>
       </c>
       <c r="E53" s="3">
         <v>103</v>
@@ -13239,8 +13319,8 @@
       <c r="C54" s="3">
         <v>1010</v>
       </c>
-      <c r="D54" s="43">
-        <v>500000000000000</v>
+      <c r="D54" s="45" t="s">
+        <v>1641</v>
       </c>
       <c r="F54" s="3">
         <v>10</v>
@@ -13274,8 +13354,8 @@
       <c r="C55" s="3">
         <v>1011</v>
       </c>
-      <c r="D55" s="43">
-        <v>4000000000000000</v>
+      <c r="D55" s="45" t="s">
+        <v>1642</v>
       </c>
       <c r="F55" s="3">
         <v>10</v>
@@ -13309,8 +13389,8 @@
       <c r="C56" s="3">
         <v>1012</v>
       </c>
-      <c r="D56" s="43">
-        <v>2E+16</v>
+      <c r="D56" s="45" t="s">
+        <v>1643</v>
       </c>
       <c r="E56" s="3">
         <v>103</v>
@@ -13347,8 +13427,8 @@
       <c r="C57" s="3">
         <v>1013</v>
       </c>
-      <c r="D57" s="43">
-        <v>1.6E+17</v>
+      <c r="D57" s="45" t="s">
+        <v>1644</v>
       </c>
       <c r="F57" s="3">
         <v>10</v>
@@ -13382,8 +13462,8 @@
       <c r="C58" s="3">
         <v>1014</v>
       </c>
-      <c r="D58" s="43">
-        <v>8E+17</v>
+      <c r="D58" s="45" t="s">
+        <v>1645</v>
       </c>
       <c r="F58" s="3">
         <v>10</v>
@@ -13417,8 +13497,8 @@
       <c r="C59" s="3">
         <v>1015</v>
       </c>
-      <c r="D59" s="43">
-        <v>6.4E+18</v>
+      <c r="D59" s="45" t="s">
+        <v>1646</v>
       </c>
       <c r="E59" s="3">
         <v>103</v>
@@ -13455,8 +13535,8 @@
       <c r="C60" s="3">
         <v>1016</v>
       </c>
-      <c r="D60" s="43">
-        <v>3.2E+19</v>
+      <c r="D60" s="45" t="s">
+        <v>1647</v>
       </c>
       <c r="F60" s="3">
         <v>10</v>
@@ -13490,8 +13570,8 @@
       <c r="C61" s="3">
         <v>1017</v>
       </c>
-      <c r="D61" s="43">
-        <v>2.56E+20</v>
+      <c r="D61" s="45" t="s">
+        <v>1648</v>
       </c>
       <c r="F61" s="3">
         <v>10</v>
@@ -13525,7 +13605,7 @@
       <c r="C62" s="3">
         <v>1018</v>
       </c>
-      <c r="D62" s="43">
+      <c r="D62" s="6">
         <v>1.28E+21</v>
       </c>
       <c r="E62" s="3">
@@ -13563,7 +13643,7 @@
       <c r="C63" s="3">
         <v>1019</v>
       </c>
-      <c r="D63" s="43">
+      <c r="D63" s="6">
         <v>1.024E+22</v>
       </c>
       <c r="F63" s="3">
@@ -13598,7 +13678,7 @@
       <c r="C64" s="3">
         <v>1020</v>
       </c>
-      <c r="D64" s="43">
+      <c r="D64" s="6">
         <v>5.12E+22</v>
       </c>
       <c r="F64" s="3">
@@ -20738,8 +20818,8 @@
       <c r="C264" s="3">
         <v>1006</v>
       </c>
-      <c r="D264" s="25">
-        <v>100354000000</v>
+      <c r="D264" s="46" t="s">
+        <v>1649</v>
       </c>
       <c r="E264" s="3">
         <v>113</v>
@@ -20776,8 +20856,8 @@
       <c r="C265" s="3">
         <v>1007</v>
       </c>
-      <c r="D265" s="25">
-        <v>1355020000000</v>
+      <c r="D265" s="46" t="s">
+        <v>1650</v>
       </c>
       <c r="F265" s="3">
         <v>10</v>
@@ -20811,8 +20891,8 @@
       <c r="C266" s="3">
         <v>1008</v>
       </c>
-      <c r="D266" s="25">
-        <v>20565900000000</v>
+      <c r="D266" s="46" t="s">
+        <v>1651</v>
       </c>
       <c r="F266" s="3">
         <v>10</v>
@@ -20846,8 +20926,8 @@
       <c r="C267" s="3">
         <v>1009</v>
       </c>
-      <c r="D267" s="25">
-        <v>348311510000000</v>
+      <c r="D267" s="46" t="s">
+        <v>1652</v>
       </c>
       <c r="E267" s="3">
         <v>113</v>
